--- a/InputData/elec/EIaE/Elec Imports and Exports.xlsx
+++ b/InputData/elec/EIaE/Elec Imports and Exports.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\elec\EIaE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\EIaE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842E961-F57D-483B-9B2C-67AB2CAD215A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E9D927-DAD9-4EC8-BF9F-2CD6C0E3D917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,9 @@
     <sheet name="EIaE-BIE" sheetId="3" r:id="rId10"/>
     <sheet name="EIaE-BEE" sheetId="5" r:id="rId11"/>
     <sheet name="EIaE-IEP" sheetId="9" r:id="rId12"/>
-    <sheet name="EIaE-BEEP" sheetId="10" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="lignite_multiplier">'[1]Hard Coal and Lig Multipliers'!$N$16</definedName>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="460">
   <si>
     <t>EIaE BAU Imported Electricity</t>
   </si>
@@ -375,9 +374,6 @@
     <t>Unit: 2012 USD/MWh</t>
   </si>
   <si>
-    <t>Exported Electricity Price</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Expenditures by Sector</t>
   </si>
   <si>
@@ -451,9 +447,6 @@
   </si>
   <si>
     <t>2050</t>
-  </si>
-  <si>
-    <t>2012 USD/2021 USD</t>
   </si>
   <si>
     <t>2012 USD/2020 USD</t>
@@ -1433,6 +1426,9 @@
   </si>
   <si>
     <t>Annual Energy Outlook 2025</t>
+  </si>
+  <si>
+    <t>2012 USD/2024 USD</t>
   </si>
 </sst>
 </file>
@@ -1441,7 +1437,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1707,7 +1703,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2920,32 +2916,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -2953,238 +2949,238 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="2">
         <v>2021</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B32" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>2.931E-7</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>0.88711067149387013</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
-        <v>0.84730412960844359</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -3204,13 +3200,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="2" customWidth="1"/>
-    <col min="2" max="28" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" style="2" customWidth="1"/>
+    <col min="2" max="28" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>103</v>
       </c>
@@ -3296,7 +3292,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
@@ -3409,9 +3405,9 @@
         <v>5475.0654336080042</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3" s="5">
         <f>calcs!B3</f>
@@ -3522,9 +3518,9 @@
         <v>3344770.2603455731</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B4" s="5">
         <f>calcs!B4</f>
@@ -3635,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
@@ -3748,7 +3744,7 @@
         <v>5934906.0595875503</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>72</v>
       </c>
@@ -3861,7 +3857,7 @@
         <v>27582653.10554963</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>71</v>
       </c>
@@ -3974,7 +3970,7 @@
         <v>11653042.280715575</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
@@ -4087,7 +4083,7 @@
         <v>3841564.0308032352</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>74</v>
       </c>
@@ -4200,7 +4196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>75</v>
       </c>
@@ -4313,7 +4309,7 @@
         <v>473161.30819733249</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -4426,7 +4422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>77</v>
       </c>
@@ -4539,7 +4535,7 @@
         <v>353432.71074296214</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>78</v>
       </c>
@@ -4652,7 +4648,7 @@
         <v>927702.17862454022</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -4765,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -4878,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>100</v>
       </c>
@@ -4991,7 +4987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
@@ -5104,7 +5100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>102</v>
       </c>
@@ -5217,9 +5213,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B19" s="5">
         <f>calcs!B19</f>
@@ -5330,9 +5326,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B20" s="5">
         <f>calcs!B20</f>
@@ -5443,9 +5439,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B21" s="5">
         <f>calcs!B21</f>
@@ -5556,9 +5552,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B22" s="5">
         <f>calcs!B22</f>
@@ -5669,9 +5665,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B23" s="5">
         <f>calcs!B23</f>
@@ -5782,9 +5778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B24" s="5">
         <f>calcs!B24</f>
@@ -5895,9 +5891,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B25" s="5">
         <f>calcs!B25</f>
@@ -6019,12 +6015,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>104</v>
       </c>
@@ -6110,7 +6106,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -6234,12 +6230,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>107</v>
       </c>
@@ -6328,345 +6324,120 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>106</v>
       </c>
       <c r="B2" s="10">
         <f>calcs!B31</f>
-        <v>110.13681138755371</v>
+        <v>95.149006264073691</v>
       </c>
       <c r="C2" s="10">
         <f>calcs!C31</f>
-        <v>107.92640565537405</v>
+        <v>93.239400327533261</v>
       </c>
       <c r="D2" s="10">
         <f>calcs!D31</f>
-        <v>100.83752570455681</v>
+        <v>87.115200122824959</v>
       </c>
       <c r="E2" s="10">
         <f>calcs!E31</f>
-        <v>95.540198209430116</v>
+        <v>82.538751606960091</v>
       </c>
       <c r="F2" s="10">
         <f>calcs!F31</f>
-        <v>95.033376783285618</v>
+        <v>82.100900225179132</v>
       </c>
       <c r="G2" s="10">
         <f>calcs!G31</f>
-        <v>96.085152657661482</v>
+        <v>83.00954673490277</v>
       </c>
       <c r="H2" s="10">
         <f>calcs!H31</f>
-        <v>97.400587259915014</v>
+        <v>84.145972364380768</v>
       </c>
       <c r="I2" s="10">
         <f>calcs!I31</f>
-        <v>99.145759137456636</v>
+        <v>85.653655107471849</v>
       </c>
       <c r="J2" s="10">
         <f>calcs!J31</f>
-        <v>100.67523126190808</v>
+        <v>86.974991279426817</v>
       </c>
       <c r="K2" s="10">
         <f>calcs!K31</f>
-        <v>102.88228651477618</v>
+        <v>88.881702681678604</v>
       </c>
       <c r="L2" s="10">
         <f>calcs!L31</f>
-        <v>103.56961754331238</v>
+        <v>89.475499283520975</v>
       </c>
       <c r="M2" s="10">
         <f>calcs!M31</f>
-        <v>103.02089055366463</v>
+        <v>89.001444994882291</v>
       </c>
       <c r="N2" s="10">
         <f>calcs!N31</f>
-        <v>102.05989561269746</v>
+        <v>88.171225629477988</v>
       </c>
       <c r="O2" s="10">
         <f>calcs!O31</f>
-        <v>101.26503414503112</v>
+        <v>87.48453170931424</v>
       </c>
       <c r="P2" s="10">
         <f>calcs!P31</f>
-        <v>101.77037546297241</v>
+        <v>87.921104401228249</v>
       </c>
       <c r="Q2" s="10">
         <f>calcs!Q31</f>
-        <v>101.11446204371831</v>
+        <v>87.354449989764589</v>
       </c>
       <c r="R2" s="10">
         <f>calcs!R31</f>
-        <v>100.80378097202554</v>
+        <v>87.086047492323431</v>
       </c>
       <c r="S2" s="10">
         <f>calcs!S31</f>
-        <v>100.84947931279949</v>
+        <v>87.125527041965185</v>
       </c>
       <c r="T2" s="10">
         <f>calcs!T31</f>
-        <v>101.33333882593998</v>
+        <v>87.543541248720558</v>
       </c>
       <c r="U2" s="10">
         <f>calcs!U31</f>
-        <v>101.79790200654843</v>
+        <v>87.944885035823944</v>
       </c>
       <c r="V2" s="10">
         <f>calcs!V31</f>
-        <v>102.39755396906273</v>
+        <v>88.462934247697049</v>
       </c>
       <c r="W2" s="10">
         <f>calcs!W31</f>
-        <v>102.86948300065119</v>
+        <v>88.870641514841353</v>
       </c>
       <c r="X2" s="10">
         <f>calcs!X31</f>
-        <v>103.37880500022492</v>
+        <v>89.31065318321393</v>
       </c>
       <c r="Y2" s="10">
         <f>calcs!Y31</f>
-        <v>103.66819506231494</v>
+        <v>89.560662026612079</v>
       </c>
       <c r="Z2" s="10">
         <f>calcs!Z31</f>
-        <v>104.40386087436207</v>
+        <v>90.196215844421687</v>
       </c>
       <c r="AA2" s="10">
         <f>calcs!AA31</f>
-        <v>105.06715170794153</v>
+        <v>90.769243725690885</v>
       </c>
       <c r="AB2" s="10">
         <f>calcs!AB31</f>
-        <v>105.86229069589598</v>
+        <v>91.456177400204723</v>
       </c>
       <c r="AC2" s="10">
         <f>calcs!AC31</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364777A9-21C3-491A-80BE-AFAA838DFA2A}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1">
-        <v>2023</v>
-      </c>
-      <c r="C1">
-        <v>2024</v>
-      </c>
-      <c r="D1">
-        <v>2025</v>
-      </c>
-      <c r="E1">
-        <v>2026</v>
-      </c>
-      <c r="F1">
-        <v>2027</v>
-      </c>
-      <c r="G1">
-        <v>2028</v>
-      </c>
-      <c r="H1">
-        <v>2029</v>
-      </c>
-      <c r="I1">
-        <v>2030</v>
-      </c>
-      <c r="J1">
-        <v>2031</v>
-      </c>
-      <c r="K1">
-        <v>2032</v>
-      </c>
-      <c r="L1">
-        <v>2033</v>
-      </c>
-      <c r="M1">
-        <v>2034</v>
-      </c>
-      <c r="N1">
-        <v>2035</v>
-      </c>
-      <c r="O1">
-        <v>2036</v>
-      </c>
-      <c r="P1">
-        <v>2037</v>
-      </c>
-      <c r="Q1">
-        <v>2038</v>
-      </c>
-      <c r="R1">
-        <v>2039</v>
-      </c>
-      <c r="S1">
-        <v>2040</v>
-      </c>
-      <c r="T1">
-        <v>2041</v>
-      </c>
-      <c r="U1">
-        <v>2042</v>
-      </c>
-      <c r="V1">
-        <v>2043</v>
-      </c>
-      <c r="W1">
-        <v>2044</v>
-      </c>
-      <c r="X1">
-        <v>2045</v>
-      </c>
-      <c r="Y1">
-        <v>2046</v>
-      </c>
-      <c r="Z1">
-        <v>2047</v>
-      </c>
-      <c r="AA1">
-        <v>2048</v>
-      </c>
-      <c r="AB1">
-        <v>2049</v>
-      </c>
-      <c r="AC1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="10">
-        <f>calcs!B34</f>
-        <v>110.13681138755371</v>
-      </c>
-      <c r="C2" s="10">
-        <f>calcs!C34</f>
-        <v>107.92640565537405</v>
-      </c>
-      <c r="D2" s="10">
-        <f>calcs!D34</f>
-        <v>100.83752570455681</v>
-      </c>
-      <c r="E2" s="10">
-        <f>calcs!E34</f>
-        <v>95.540198209430116</v>
-      </c>
-      <c r="F2" s="10">
-        <f>calcs!F34</f>
-        <v>95.033376783285618</v>
-      </c>
-      <c r="G2" s="10">
-        <f>calcs!G34</f>
-        <v>96.085152657661482</v>
-      </c>
-      <c r="H2" s="10">
-        <f>calcs!H34</f>
-        <v>97.400587259915014</v>
-      </c>
-      <c r="I2" s="10">
-        <f>calcs!I34</f>
-        <v>99.145759137456636</v>
-      </c>
-      <c r="J2" s="10">
-        <f>calcs!J34</f>
-        <v>100.67523126190808</v>
-      </c>
-      <c r="K2" s="10">
-        <f>calcs!K34</f>
-        <v>102.88228651477618</v>
-      </c>
-      <c r="L2" s="10">
-        <f>calcs!L34</f>
-        <v>103.56961754331238</v>
-      </c>
-      <c r="M2" s="10">
-        <f>calcs!M34</f>
-        <v>103.02089055366463</v>
-      </c>
-      <c r="N2" s="10">
-        <f>calcs!N34</f>
-        <v>102.05989561269746</v>
-      </c>
-      <c r="O2" s="10">
-        <f>calcs!O34</f>
-        <v>101.26503414503112</v>
-      </c>
-      <c r="P2" s="10">
-        <f>calcs!P34</f>
-        <v>101.77037546297241</v>
-      </c>
-      <c r="Q2" s="10">
-        <f>calcs!Q34</f>
-        <v>101.11446204371831</v>
-      </c>
-      <c r="R2" s="10">
-        <f>calcs!R34</f>
-        <v>100.80378097202554</v>
-      </c>
-      <c r="S2" s="10">
-        <f>calcs!S34</f>
-        <v>100.84947931279949</v>
-      </c>
-      <c r="T2" s="10">
-        <f>calcs!T34</f>
-        <v>101.33333882593998</v>
-      </c>
-      <c r="U2" s="10">
-        <f>calcs!U34</f>
-        <v>101.79790200654843</v>
-      </c>
-      <c r="V2" s="10">
-        <f>calcs!V34</f>
-        <v>102.39755396906273</v>
-      </c>
-      <c r="W2" s="10">
-        <f>calcs!W34</f>
-        <v>102.86948300065119</v>
-      </c>
-      <c r="X2" s="10">
-        <f>calcs!X34</f>
-        <v>103.37880500022492</v>
-      </c>
-      <c r="Y2" s="10">
-        <f>calcs!Y34</f>
-        <v>103.66819506231494</v>
-      </c>
-      <c r="Z2" s="10">
-        <f>calcs!Z34</f>
-        <v>104.40386087436207</v>
-      </c>
-      <c r="AA2" s="10">
-        <f>calcs!AA34</f>
-        <v>105.06715170794153</v>
-      </c>
-      <c r="AB2" s="10">
-        <f>calcs!AB34</f>
-        <v>105.86229069589598</v>
-      </c>
-      <c r="AC2" s="10">
-        <f>calcs!AC34</f>
         <v>0</v>
       </c>
       <c r="AD2" s="10"/>
@@ -6684,7 +6455,7 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6693,41 +6464,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F094CE8E-5EA4-4A10-AEAF-2F4998C50D06}">
   <dimension ref="A1:AG23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="90.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="90.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E5">
         <v>2023</v>
@@ -6814,31 +6585,31 @@
         <v>2050</v>
       </c>
       <c r="AG5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F8">
         <v>45.122737999999998</v>
@@ -6925,18 +6696,18 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F9">
         <v>249.34066799999999</v>
@@ -7023,18 +6794,18 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F10">
         <v>294.46337899999997</v>
@@ -7121,23 +6892,23 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F12">
         <v>3718.7072750000002</v>
@@ -7224,18 +6995,18 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F13">
         <v>10351.311523</v>
@@ -7322,18 +7093,18 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F14">
         <v>14070.018555000001</v>
@@ -7420,28 +7191,28 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F17">
         <v>16.437441</v>
@@ -7528,18 +7299,18 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F18" s="17">
         <v>29.155847999999999</v>
@@ -7626,18 +7397,18 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F19">
         <v>45.593288000000001</v>
@@ -7724,23 +7495,23 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F21">
         <v>1.19574</v>
@@ -7827,18 +7598,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F22" s="17">
         <v>14.989228000000001</v>
@@ -7925,18 +7696,18 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F23">
         <v>16.184968999999999</v>
@@ -8031,37 +7802,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AU159"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47" ht="21" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:47" ht="21" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -8174,37 +7945,37 @@
         <v>47</v>
       </c>
       <c r="AL8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM8" t="s">
         <v>124</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AN8" t="s">
         <v>125</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>126</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AP8" t="s">
         <v>127</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AQ8" t="s">
         <v>128</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>129</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AS8" t="s">
         <v>130</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="AT8" t="s">
         <v>131</v>
       </c>
-      <c r="AT8" t="s">
+      <c r="AU8" t="s">
         <v>132</v>
       </c>
-      <c r="AU8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -8347,7 +8118,7 @@
         <v>446455.8</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -8490,7 +8261,7 @@
         <v>188617.4</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -8633,7 +8404,7 @@
         <v>7658.64</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -8776,7 +8547,7 @@
         <v>62179.97</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -8919,7 +8690,7 @@
         <v>96063.03</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -9062,7 +8833,7 @@
         <v>88.62</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -9205,7 +8976,7 @@
         <v>69154.7</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -9348,12 +9119,12 @@
         <v>5720.7</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -9466,37 +9237,37 @@
         <v>47</v>
       </c>
       <c r="AL19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM19" t="s">
         <v>124</v>
       </c>
-      <c r="AM19" t="s">
+      <c r="AN19" t="s">
         <v>125</v>
       </c>
-      <c r="AN19" t="s">
+      <c r="AO19" t="s">
         <v>126</v>
       </c>
-      <c r="AO19" t="s">
+      <c r="AP19" t="s">
         <v>127</v>
       </c>
-      <c r="AP19" t="s">
+      <c r="AQ19" t="s">
         <v>128</v>
       </c>
-      <c r="AQ19" t="s">
+      <c r="AR19" t="s">
         <v>129</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="AS19" t="s">
         <v>130</v>
       </c>
-      <c r="AS19" t="s">
+      <c r="AT19" t="s">
         <v>131</v>
       </c>
-      <c r="AT19" t="s">
+      <c r="AU19" t="s">
         <v>132</v>
       </c>
-      <c r="AU19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -9639,7 +9410,7 @@
         <v>52458.85</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -9782,7 +9553,7 @@
         <v>982.55</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -9925,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -10068,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -10211,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -10354,7 +10125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -10497,7 +10268,7 @@
         <v>1413.07</v>
       </c>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -10640,12 +10411,12 @@
         <v>189.45</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A29" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -10758,37 +10529,37 @@
         <v>47</v>
       </c>
       <c r="AL30" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM30" t="s">
         <v>124</v>
       </c>
-      <c r="AM30" t="s">
+      <c r="AN30" t="s">
         <v>125</v>
       </c>
-      <c r="AN30" t="s">
+      <c r="AO30" t="s">
         <v>126</v>
       </c>
-      <c r="AO30" t="s">
+      <c r="AP30" t="s">
         <v>127</v>
       </c>
-      <c r="AP30" t="s">
+      <c r="AQ30" t="s">
         <v>128</v>
       </c>
-      <c r="AQ30" t="s">
+      <c r="AR30" t="s">
         <v>129</v>
       </c>
-      <c r="AR30" t="s">
+      <c r="AS30" t="s">
         <v>130</v>
       </c>
-      <c r="AS30" t="s">
+      <c r="AT30" t="s">
         <v>131</v>
       </c>
-      <c r="AT30" t="s">
+      <c r="AU30" t="s">
         <v>132</v>
       </c>
-      <c r="AU30" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -10931,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -11074,7 +10845,7 @@
         <v>1885.59</v>
       </c>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -11217,7 +10988,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -11360,7 +11131,7 @@
         <v>160.61000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -11503,7 +11274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -11646,7 +11417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -11789,7 +11560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -11932,12 +11703,12 @@
         <v>48.27</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A40" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -12050,37 +11821,37 @@
         <v>47</v>
       </c>
       <c r="AL41" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM41" t="s">
         <v>124</v>
       </c>
-      <c r="AM41" t="s">
+      <c r="AN41" t="s">
         <v>125</v>
       </c>
-      <c r="AN41" t="s">
+      <c r="AO41" t="s">
         <v>126</v>
       </c>
-      <c r="AO41" t="s">
+      <c r="AP41" t="s">
         <v>127</v>
       </c>
-      <c r="AP41" t="s">
+      <c r="AQ41" t="s">
         <v>128</v>
       </c>
-      <c r="AQ41" t="s">
+      <c r="AR41" t="s">
         <v>129</v>
       </c>
-      <c r="AR41" t="s">
+      <c r="AS41" t="s">
         <v>130</v>
       </c>
-      <c r="AS41" t="s">
+      <c r="AT41" t="s">
         <v>131</v>
       </c>
-      <c r="AT41" t="s">
+      <c r="AU41" t="s">
         <v>132</v>
       </c>
-      <c r="AU41" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -12223,7 +11994,7 @@
         <v>1207.82</v>
       </c>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -12366,7 +12137,7 @@
         <v>3954</v>
       </c>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>50</v>
       </c>
@@ -12509,7 +12280,7 @@
         <v>200.63</v>
       </c>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>51</v>
       </c>
@@ -12652,7 +12423,7 @@
         <v>528.46</v>
       </c>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>52</v>
       </c>
@@ -12795,7 +12566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -12938,7 +12709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -13081,7 +12852,7 @@
         <v>2932.47</v>
       </c>
     </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -13224,12 +12995,12 @@
         <v>407.56</v>
       </c>
     </row>
-    <row r="51" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A51" s="12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -13342,37 +13113,37 @@
         <v>47</v>
       </c>
       <c r="AL52" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM52" t="s">
         <v>124</v>
       </c>
-      <c r="AM52" t="s">
+      <c r="AN52" t="s">
         <v>125</v>
       </c>
-      <c r="AN52" t="s">
+      <c r="AO52" t="s">
         <v>126</v>
       </c>
-      <c r="AO52" t="s">
+      <c r="AP52" t="s">
         <v>127</v>
       </c>
-      <c r="AP52" t="s">
+      <c r="AQ52" t="s">
         <v>128</v>
       </c>
-      <c r="AQ52" t="s">
+      <c r="AR52" t="s">
         <v>129</v>
       </c>
-      <c r="AR52" t="s">
+      <c r="AS52" t="s">
         <v>130</v>
       </c>
-      <c r="AS52" t="s">
+      <c r="AT52" t="s">
         <v>131</v>
       </c>
-      <c r="AT52" t="s">
+      <c r="AU52" t="s">
         <v>132</v>
       </c>
-      <c r="AU52" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -13515,7 +13286,7 @@
         <v>3123.74</v>
       </c>
     </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -13658,7 +13429,7 @@
         <v>3743.52</v>
       </c>
     </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -13801,7 +13572,7 @@
         <v>509.39</v>
       </c>
     </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>51</v>
       </c>
@@ -13944,7 +13715,7 @@
         <v>1042.67</v>
       </c>
     </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -14087,7 +13858,7 @@
         <v>5353.24</v>
       </c>
     </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -14230,7 +14001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -14373,7 +14144,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -14516,12 +14287,12 @@
         <v>90.41</v>
       </c>
     </row>
-    <row r="62" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A62" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -14634,37 +14405,37 @@
         <v>47</v>
       </c>
       <c r="AL63" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM63" t="s">
         <v>124</v>
       </c>
-      <c r="AM63" t="s">
+      <c r="AN63" t="s">
         <v>125</v>
       </c>
-      <c r="AN63" t="s">
+      <c r="AO63" t="s">
         <v>126</v>
       </c>
-      <c r="AO63" t="s">
+      <c r="AP63" t="s">
         <v>127</v>
       </c>
-      <c r="AP63" t="s">
+      <c r="AQ63" t="s">
         <v>128</v>
       </c>
-      <c r="AQ63" t="s">
+      <c r="AR63" t="s">
         <v>129</v>
       </c>
-      <c r="AR63" t="s">
+      <c r="AS63" t="s">
         <v>130</v>
       </c>
-      <c r="AS63" t="s">
+      <c r="AT63" t="s">
         <v>131</v>
       </c>
-      <c r="AT63" t="s">
+      <c r="AU63" t="s">
         <v>132</v>
       </c>
-      <c r="AU63" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>48</v>
       </c>
@@ -14807,7 +14578,7 @@
         <v>217546.8</v>
       </c>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>49</v>
       </c>
@@ -14950,7 +14721,7 @@
         <v>29345.68</v>
       </c>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>50</v>
       </c>
@@ -15093,7 +14864,7 @@
         <v>1557.93</v>
       </c>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -15236,7 +15007,7 @@
         <v>9235.25</v>
       </c>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>52</v>
       </c>
@@ -15379,7 +15150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -15522,7 +15293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -15665,7 +15436,7 @@
         <v>186.63</v>
       </c>
     </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -15808,12 +15579,12 @@
         <v>402.43</v>
       </c>
     </row>
-    <row r="73" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -15926,37 +15697,37 @@
         <v>47</v>
       </c>
       <c r="AL74" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM74" t="s">
         <v>124</v>
       </c>
-      <c r="AM74" t="s">
+      <c r="AN74" t="s">
         <v>125</v>
       </c>
-      <c r="AN74" t="s">
+      <c r="AO74" t="s">
         <v>126</v>
       </c>
-      <c r="AO74" t="s">
+      <c r="AP74" t="s">
         <v>127</v>
       </c>
-      <c r="AP74" t="s">
+      <c r="AQ74" t="s">
         <v>128</v>
       </c>
-      <c r="AQ74" t="s">
+      <c r="AR74" t="s">
         <v>129</v>
       </c>
-      <c r="AR74" t="s">
+      <c r="AS74" t="s">
         <v>130</v>
       </c>
-      <c r="AS74" t="s">
+      <c r="AT74" t="s">
         <v>131</v>
       </c>
-      <c r="AT74" t="s">
+      <c r="AU74" t="s">
         <v>132</v>
       </c>
-      <c r="AU74" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="75" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -16099,7 +15870,7 @@
         <v>42724.63</v>
       </c>
     </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>49</v>
       </c>
@@ -16242,7 +16013,7 @@
         <v>73400.41</v>
       </c>
     </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>50</v>
       </c>
@@ -16385,7 +16156,7 @@
         <v>783.61</v>
       </c>
     </row>
-    <row r="78" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>51</v>
       </c>
@@ -16528,7 +16299,7 @@
         <v>30297.55</v>
       </c>
     </row>
-    <row r="79" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>52</v>
       </c>
@@ -16671,7 +16442,7 @@
         <v>90709.79</v>
       </c>
     </row>
-    <row r="80" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>53</v>
       </c>
@@ -16814,7 +16585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>54</v>
       </c>
@@ -16957,7 +16728,7 @@
         <v>4852.41</v>
       </c>
     </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -17100,12 +16871,12 @@
         <v>4029.9</v>
       </c>
     </row>
-    <row r="84" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A84" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -17218,37 +16989,37 @@
         <v>47</v>
       </c>
       <c r="AL85" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM85" t="s">
         <v>124</v>
       </c>
-      <c r="AM85" t="s">
+      <c r="AN85" t="s">
         <v>125</v>
       </c>
-      <c r="AN85" t="s">
+      <c r="AO85" t="s">
         <v>126</v>
       </c>
-      <c r="AO85" t="s">
+      <c r="AP85" t="s">
         <v>127</v>
       </c>
-      <c r="AP85" t="s">
+      <c r="AQ85" t="s">
         <v>128</v>
       </c>
-      <c r="AQ85" t="s">
+      <c r="AR85" t="s">
         <v>129</v>
       </c>
-      <c r="AR85" t="s">
+      <c r="AS85" t="s">
         <v>130</v>
       </c>
-      <c r="AS85" t="s">
+      <c r="AT85" t="s">
         <v>131</v>
       </c>
-      <c r="AT85" t="s">
+      <c r="AU85" t="s">
         <v>132</v>
       </c>
-      <c r="AU85" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>48</v>
       </c>
@@ -17391,7 +17162,7 @@
         <v>39040.559999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>49</v>
       </c>
@@ -17534,7 +17305,7 @@
         <v>6301.06</v>
       </c>
     </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>50</v>
       </c>
@@ -17677,7 +17448,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>51</v>
       </c>
@@ -17820,7 +17591,7 @@
         <v>2353.86</v>
       </c>
     </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>52</v>
       </c>
@@ -17963,7 +17734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>53</v>
       </c>
@@ -18106,7 +17877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>54</v>
       </c>
@@ -18249,7 +18020,7 @@
         <v>168.86</v>
       </c>
     </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>55</v>
       </c>
@@ -18392,12 +18163,12 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="95" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -18510,37 +18281,37 @@
         <v>47</v>
       </c>
       <c r="AL96" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM96" t="s">
         <v>124</v>
       </c>
-      <c r="AM96" t="s">
+      <c r="AN96" t="s">
         <v>125</v>
       </c>
-      <c r="AN96" t="s">
+      <c r="AO96" t="s">
         <v>126</v>
       </c>
-      <c r="AO96" t="s">
+      <c r="AP96" t="s">
         <v>127</v>
       </c>
-      <c r="AP96" t="s">
+      <c r="AQ96" t="s">
         <v>128</v>
       </c>
-      <c r="AQ96" t="s">
+      <c r="AR96" t="s">
         <v>129</v>
       </c>
-      <c r="AR96" t="s">
+      <c r="AS96" t="s">
         <v>130</v>
       </c>
-      <c r="AS96" t="s">
+      <c r="AT96" t="s">
         <v>131</v>
       </c>
-      <c r="AT96" t="s">
+      <c r="AU96" t="s">
         <v>132</v>
       </c>
-      <c r="AU96" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="97" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>48</v>
       </c>
@@ -18683,7 +18454,7 @@
         <v>505.55</v>
       </c>
     </row>
-    <row r="98" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>49</v>
       </c>
@@ -18826,7 +18597,7 @@
         <v>35844.17</v>
       </c>
     </row>
-    <row r="99" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>50</v>
       </c>
@@ -18969,7 +18740,7 @@
         <v>1278.17</v>
       </c>
     </row>
-    <row r="100" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>51</v>
       </c>
@@ -19112,7 +18883,7 @@
         <v>8876.16</v>
       </c>
     </row>
-    <row r="101" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>52</v>
       </c>
@@ -19255,7 +19026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>53</v>
       </c>
@@ -19398,7 +19169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>54</v>
       </c>
@@ -19541,7 +19312,7 @@
         <v>49880.18</v>
       </c>
     </row>
-    <row r="104" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>55</v>
       </c>
@@ -19684,12 +19455,12 @@
         <v>19.079999999999998</v>
       </c>
     </row>
-    <row r="106" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -19802,37 +19573,37 @@
         <v>47</v>
       </c>
       <c r="AL107" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM107" t="s">
         <v>124</v>
       </c>
-      <c r="AM107" t="s">
+      <c r="AN107" t="s">
         <v>125</v>
       </c>
-      <c r="AN107" t="s">
+      <c r="AO107" t="s">
         <v>126</v>
       </c>
-      <c r="AO107" t="s">
+      <c r="AP107" t="s">
         <v>127</v>
       </c>
-      <c r="AP107" t="s">
+      <c r="AQ107" t="s">
         <v>128</v>
       </c>
-      <c r="AQ107" t="s">
+      <c r="AR107" t="s">
         <v>129</v>
       </c>
-      <c r="AR107" t="s">
+      <c r="AS107" t="s">
         <v>130</v>
       </c>
-      <c r="AS107" t="s">
+      <c r="AT107" t="s">
         <v>131</v>
       </c>
-      <c r="AT107" t="s">
+      <c r="AU107" t="s">
         <v>132</v>
       </c>
-      <c r="AU107" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>48</v>
       </c>
@@ -19975,7 +19746,7 @@
         <v>86796.58</v>
       </c>
     </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>49</v>
       </c>
@@ -20118,7 +19889,7 @@
         <v>19386.72</v>
       </c>
     </row>
-    <row r="110" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>50</v>
       </c>
@@ -20261,7 +20032,7 @@
         <v>3129.69</v>
       </c>
     </row>
-    <row r="111" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>51</v>
       </c>
@@ -20404,7 +20175,7 @@
         <v>8396.49</v>
       </c>
     </row>
-    <row r="112" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>52</v>
       </c>
@@ -20547,7 +20318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>53</v>
       </c>
@@ -20690,7 +20461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>54</v>
       </c>
@@ -20833,7 +20604,7 @@
         <v>2433.8200000000002</v>
       </c>
     </row>
-    <row r="115" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>55</v>
       </c>
@@ -20976,12 +20747,12 @@
         <v>171.47</v>
       </c>
     </row>
-    <row r="117" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A117" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="118" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -21094,37 +20865,37 @@
         <v>47</v>
       </c>
       <c r="AL118" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM118" t="s">
         <v>124</v>
       </c>
-      <c r="AM118" t="s">
+      <c r="AN118" t="s">
         <v>125</v>
       </c>
-      <c r="AN118" t="s">
+      <c r="AO118" t="s">
         <v>126</v>
       </c>
-      <c r="AO118" t="s">
+      <c r="AP118" t="s">
         <v>127</v>
       </c>
-      <c r="AP118" t="s">
+      <c r="AQ118" t="s">
         <v>128</v>
       </c>
-      <c r="AQ118" t="s">
+      <c r="AR118" t="s">
         <v>129</v>
       </c>
-      <c r="AR118" t="s">
+      <c r="AS118" t="s">
         <v>130</v>
       </c>
-      <c r="AS118" t="s">
+      <c r="AT118" t="s">
         <v>131</v>
       </c>
-      <c r="AT118" t="s">
+      <c r="AU118" t="s">
         <v>132</v>
       </c>
-      <c r="AU118" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="119" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>48</v>
       </c>
@@ -21267,7 +21038,7 @@
         <v>2285.31</v>
       </c>
     </row>
-    <row r="120" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>49</v>
       </c>
@@ -21410,7 +21181,7 @@
         <v>13656.86</v>
       </c>
     </row>
-    <row r="121" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>50</v>
       </c>
@@ -21553,7 +21324,7 @@
         <v>112.74</v>
       </c>
     </row>
-    <row r="122" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>51</v>
       </c>
@@ -21696,7 +21467,7 @@
         <v>1251.07</v>
       </c>
     </row>
-    <row r="123" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>52</v>
       </c>
@@ -21839,7 +21610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>53</v>
       </c>
@@ -21982,7 +21753,7 @@
         <v>88.62</v>
       </c>
     </row>
-    <row r="125" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>54</v>
       </c>
@@ -22125,7 +21896,7 @@
         <v>7200.9</v>
       </c>
     </row>
-    <row r="126" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>55</v>
       </c>
@@ -22268,12 +22039,12 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="128" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A128" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -22386,37 +22157,37 @@
         <v>47</v>
       </c>
       <c r="AL129" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM129" t="s">
         <v>124</v>
       </c>
-      <c r="AM129" t="s">
+      <c r="AN129" t="s">
         <v>125</v>
       </c>
-      <c r="AN129" t="s">
+      <c r="AO129" t="s">
         <v>126</v>
       </c>
-      <c r="AO129" t="s">
+      <c r="AP129" t="s">
         <v>127</v>
       </c>
-      <c r="AP129" t="s">
+      <c r="AQ129" t="s">
         <v>128</v>
       </c>
-      <c r="AQ129" t="s">
+      <c r="AR129" t="s">
         <v>129</v>
       </c>
-      <c r="AR129" t="s">
+      <c r="AS129" t="s">
         <v>130</v>
       </c>
-      <c r="AS129" t="s">
+      <c r="AT129" t="s">
         <v>131</v>
       </c>
-      <c r="AT129" t="s">
+      <c r="AU129" t="s">
         <v>132</v>
       </c>
-      <c r="AU129" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="130" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>48</v>
       </c>
@@ -22559,7 +22330,7 @@
         <v>471.9</v>
       </c>
     </row>
-    <row r="131" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>49</v>
       </c>
@@ -22702,7 +22473,7 @@
         <v>64.64</v>
       </c>
     </row>
-    <row r="132" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>50</v>
       </c>
@@ -22845,7 +22616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>51</v>
       </c>
@@ -22988,7 +22759,7 @@
         <v>10.85</v>
       </c>
     </row>
-    <row r="134" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>52</v>
       </c>
@@ -23131,7 +22902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>53</v>
       </c>
@@ -23274,7 +23045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>54</v>
       </c>
@@ -23417,7 +23188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>55</v>
       </c>
@@ -23560,12 +23331,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A139" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="140" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -23678,37 +23449,37 @@
         <v>47</v>
       </c>
       <c r="AL140" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM140" t="s">
         <v>124</v>
       </c>
-      <c r="AM140" t="s">
+      <c r="AN140" t="s">
         <v>125</v>
       </c>
-      <c r="AN140" t="s">
+      <c r="AO140" t="s">
         <v>126</v>
       </c>
-      <c r="AO140" t="s">
+      <c r="AP140" t="s">
         <v>127</v>
       </c>
-      <c r="AP140" t="s">
+      <c r="AQ140" t="s">
         <v>128</v>
       </c>
-      <c r="AQ140" t="s">
+      <c r="AR140" t="s">
         <v>129</v>
       </c>
-      <c r="AR140" t="s">
+      <c r="AS140" t="s">
         <v>130</v>
       </c>
-      <c r="AS140" t="s">
+      <c r="AT140" t="s">
         <v>131</v>
       </c>
-      <c r="AT140" t="s">
+      <c r="AU140" t="s">
         <v>132</v>
       </c>
-      <c r="AU140" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="141" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>48</v>
       </c>
@@ -23851,7 +23622,7 @@
         <v>294.02999999999997</v>
       </c>
     </row>
-    <row r="142" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>49</v>
       </c>
@@ -23994,7 +23765,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="143" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>50</v>
       </c>
@@ -24137,7 +23908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>51</v>
       </c>
@@ -24280,7 +24051,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="145" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>52</v>
       </c>
@@ -24423,7 +24194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>53</v>
       </c>
@@ -24566,7 +24337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>54</v>
       </c>
@@ -24709,7 +24480,7 @@
         <v>86.34</v>
       </c>
     </row>
-    <row r="148" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>55</v>
       </c>
@@ -24852,12 +24623,12 @@
         <v>31.42</v>
       </c>
     </row>
-    <row r="150" spans="1:47" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:47" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A150" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="151" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -24970,37 +24741,37 @@
         <v>47</v>
       </c>
       <c r="AL151" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM151" t="s">
         <v>124</v>
       </c>
-      <c r="AM151" t="s">
+      <c r="AN151" t="s">
         <v>125</v>
       </c>
-      <c r="AN151" t="s">
+      <c r="AO151" t="s">
         <v>126</v>
       </c>
-      <c r="AO151" t="s">
+      <c r="AP151" t="s">
         <v>127</v>
       </c>
-      <c r="AP151" t="s">
+      <c r="AQ151" t="s">
         <v>128</v>
       </c>
-      <c r="AQ151" t="s">
+      <c r="AR151" t="s">
         <v>129</v>
       </c>
-      <c r="AR151" t="s">
+      <c r="AS151" t="s">
         <v>130</v>
       </c>
-      <c r="AS151" t="s">
+      <c r="AT151" t="s">
         <v>131</v>
       </c>
-      <c r="AT151" t="s">
+      <c r="AU151" t="s">
         <v>132</v>
       </c>
-      <c r="AU151" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="152" spans="1:47" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>48</v>
       </c>
@@ -25143,7 +24914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>49</v>
       </c>
@@ -25286,7 +25057,7 @@
         <v>26.73</v>
       </c>
     </row>
-    <row r="154" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>50</v>
       </c>
@@ -25429,7 +25200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>51</v>
       </c>
@@ -25572,7 +25343,7 @@
         <v>14.35</v>
       </c>
     </row>
-    <row r="156" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>52</v>
       </c>
@@ -25715,7 +25486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>53</v>
       </c>
@@ -25858,7 +25629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>54</v>
       </c>
@@ -26001,7 +25772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>55</v>
       </c>
@@ -26168,57 +25939,57 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13728A83-B067-4638-A52F-4A7CB86CF44F}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="13" width="15.7265625" customWidth="1"/>
+    <col min="14" max="14" width="27.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>144</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>147</v>
       </c>
       <c r="B11" s="13">
         <v>42005</v>
@@ -26257,17 +26028,17 @@
         <v>42339</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B13" s="14">
         <v>57211066</v>
@@ -26310,9 +26081,9 @@
         <v>550012957</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B14" s="14">
         <v>37669235</v>
@@ -26355,9 +26126,9 @@
         <v>347385073</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B15" s="14">
         <v>7190066</v>
@@ -26400,9 +26171,9 @@
         <v>74488277</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B16" s="14">
         <v>9180622</v>
@@ -26445,9 +26216,9 @@
         <v>98374974</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B17" s="14">
         <v>92383</v>
@@ -26490,9 +26261,9 @@
         <v>900163</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B18" s="14">
         <v>2014274</v>
@@ -26535,53 +26306,53 @@
         <v>19759832</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>155</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="M19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="N19" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>157</v>
       </c>
       <c r="B20">
         <v>-124</v>
@@ -26624,9 +26395,9 @@
         <v>12820</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B21" s="14">
         <v>1053353</v>
@@ -26669,9 +26440,9 @@
         <v>8833017</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B22" s="14">
         <v>11257</v>
@@ -26714,206 +26485,206 @@
         <v>258815</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="N23" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>156</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>163</v>
       </c>
-      <c r="B27" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>12</v>
       </c>
       <c r="B44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="16" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>181</v>
-      </c>
       <c r="B52" s="17"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B53">
         <f>N15/SUM(N15,N17:N18)</f>
         <v>0.78286526317577265</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>78</v>
       </c>
@@ -26931,12 +26702,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -27031,7 +26802,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
@@ -27160,9 +26931,9 @@
         <v>1.0117144477412501E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3">
         <f>'Canada Generation Projection'!Q$15/B$20*'Canada NG Gen by Turbine Type'!$B$53</f>
@@ -27289,9 +27060,9 @@
         <v>6.1806611040571502E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B4">
         <f>'Canada Generation Projection'!Q$15/B$20*'Canada NG Gen by Turbine Type'!$B$54</f>
@@ -27418,7 +27189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
@@ -27547,7 +27318,7 @@
         <v>0.10966864742135086</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>72</v>
       </c>
@@ -27676,7 +27447,7 @@
         <v>0.50968831317747454</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>71</v>
       </c>
@@ -27805,7 +27576,7 @@
         <v>0.21533169563912261</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
@@ -27934,7 +27705,7 @@
         <v>7.0986655392820466E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>74</v>
       </c>
@@ -28032,7 +27803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>75</v>
       </c>
@@ -28161,7 +27932,7 @@
         <v>8.7433499639461149E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -28259,7 +28030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>77</v>
       </c>
@@ -28388,7 +28159,7 @@
         <v>6.5309352755510818E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>78</v>
       </c>
@@ -28517,7 +28288,7 @@
         <v>1.7142620644388807E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -28615,7 +28386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -28713,7 +28484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>100</v>
       </c>
@@ -28811,7 +28582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
@@ -28909,7 +28680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>102</v>
       </c>
@@ -29007,7 +28778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>99</v>
       </c>
@@ -29144,41 +28915,41 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00253E5B-DFBA-42D2-9616-F03E586149AF}">
   <dimension ref="A1:AG121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="54.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="54.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E5">
         <v>2023</v>
@@ -29265,26 +29036,26 @@
         <v>2050</v>
       </c>
       <c r="AG5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F7">
         <v>26.593980999999999</v>
@@ -29371,18 +29142,18 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F8">
         <v>26.158379</v>
@@ -29469,18 +29240,18 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F9">
         <v>13.932205</v>
@@ -29567,18 +29338,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C10" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F10">
         <v>45.553139000000002</v>
@@ -29665,23 +29436,23 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F12">
         <v>19.0868</v>
@@ -29768,18 +29539,18 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F13">
         <v>26.207932</v>
@@ -29866,18 +29637,18 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C14" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F14">
         <v>6.7460779999999998</v>
@@ -29964,18 +29735,18 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F15">
         <v>9.5558580000000006</v>
@@ -30062,18 +29833,18 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C16" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F16">
         <v>38.551605000000002</v>
@@ -30160,23 +29931,23 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B18" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F18">
         <v>12.660259999999999</v>
@@ -30263,18 +30034,18 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B19" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C19" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F19">
         <v>26.091763</v>
@@ -30361,18 +30132,18 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D20" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F20">
         <v>7.8346600000000004</v>
@@ -30459,18 +30230,18 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C21" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F21">
         <v>3.3370700000000002</v>
@@ -30557,18 +30328,18 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C22" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F22">
         <v>7.7677550000000002</v>
@@ -30655,18 +30426,18 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C23" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D23" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F23">
         <v>3.572155</v>
@@ -30753,18 +30524,18 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C24" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D24" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F24">
         <v>9.5338750000000001</v>
@@ -30851,18 +30622,18 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C25" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F25">
         <v>26.507746000000001</v>
@@ -30949,23 +30720,23 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C27" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D27" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F27">
         <v>17.589244999999998</v>
@@ -31052,18 +30823,18 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C28" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F28">
         <v>28.823729</v>
@@ -31150,18 +30921,18 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D29" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F29">
         <v>28.679842000000001</v>
@@ -31248,18 +31019,18 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C30" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D30" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F30">
         <v>17.638923999999999</v>
@@ -31346,18 +31117,18 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C31" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D31" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F31">
         <v>27.283649</v>
@@ -31444,18 +31215,18 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C32" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D32" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F32">
         <v>13.401297</v>
@@ -31542,18 +31313,18 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C33" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D33" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F33">
         <v>14.514303</v>
@@ -31640,18 +31411,18 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F34">
         <v>60.468231000000003</v>
@@ -31738,18 +31509,18 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B35" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C35" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D35" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F35">
         <v>42.609589</v>
@@ -31836,23 +31607,23 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C37" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F37">
         <v>26.137505000000001</v>
@@ -31939,18 +31710,18 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B38" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C38" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D38" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F38">
         <v>17.394409</v>
@@ -32037,18 +31808,18 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C39" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F39">
         <v>2.7193990000000001</v>
@@ -32135,18 +31906,18 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C40" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D40" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F40">
         <v>2.4893969999999999</v>
@@ -32233,18 +32004,18 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C41" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D41" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F41">
         <v>0.753328</v>
@@ -32331,18 +32102,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C42" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D42" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F42">
         <v>9.5338750000000001</v>
@@ -32429,23 +32200,23 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B44" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C44" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D44" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F44">
         <v>23.109310000000001</v>
@@ -32532,18 +32303,18 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B45" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C45" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D45" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F45">
         <v>28.823729</v>
@@ -32630,18 +32401,18 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B46" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D46" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F46">
         <v>28.684215999999999</v>
@@ -32728,18 +32499,18 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B47" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C47" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D47" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F47">
         <v>17.638923999999999</v>
@@ -32826,18 +32597,18 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C48" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D48" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F48">
         <v>27.012423999999999</v>
@@ -32924,18 +32695,18 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B49" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C49" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D49" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F49">
         <v>13.291615</v>
@@ -33022,18 +32793,18 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C50" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D50" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F50">
         <v>5.3580649999999999</v>
@@ -33120,18 +32891,18 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C51" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D51" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F51">
         <v>7.7677550000000002</v>
@@ -33218,18 +32989,18 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B52" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C52" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D52" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F52">
         <v>2.5446469999999999</v>
@@ -33316,18 +33087,18 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B53" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C53" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D53" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F53">
         <v>9.5735130000000002</v>
@@ -33414,18 +33185,18 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F54" s="17">
         <v>38.098598000000003</v>
@@ -33512,28 +33283,28 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C57" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D57" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F57">
         <v>321.87133799999998</v>
@@ -33620,18 +33391,18 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B58" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C58" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D58" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F58">
         <v>241.12788399999999</v>
@@ -33718,18 +33489,18 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B59" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C59" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D59" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F59">
         <v>225.60749799999999</v>
@@ -33816,18 +33587,18 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B60" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C60" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D60" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F60">
         <v>714.84161400000005</v>
@@ -33914,18 +33685,18 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B61" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C61" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D61" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F61">
         <v>1503.4482419999999</v>
@@ -34012,18 +33783,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C62" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D62" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F62">
         <v>0.107875</v>
@@ -34110,18 +33881,18 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B63" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C63" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D63" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F63">
         <v>1503.5561520000001</v>
@@ -34208,28 +33979,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B66" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C66" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D66" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F66">
         <v>26.593980999999999</v>
@@ -34316,18 +34087,18 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B67" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C67" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D67" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F67">
         <v>26.158379</v>
@@ -34414,18 +34185,18 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>54</v>
       </c>
       <c r="B68" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C68" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F68">
         <v>13.932205</v>
@@ -34512,18 +34283,18 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B69" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C69" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D69" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F69">
         <v>45.553139000000002</v>
@@ -34610,23 +34381,23 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C71" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D71" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F71">
         <v>19.0868</v>
@@ -34713,18 +34484,18 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B72" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C72" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D72" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F72">
         <v>26.207932</v>
@@ -34811,18 +34582,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C73" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D73" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F73">
         <v>6.7460779999999998</v>
@@ -34909,18 +34680,18 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C74" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D74" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F74">
         <v>9.5558580000000006</v>
@@ -35007,18 +34778,18 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B75" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C75" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D75" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F75">
         <v>38.551605000000002</v>
@@ -35105,23 +34876,23 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B77" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C77" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D77" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F77">
         <v>12.660259999999999</v>
@@ -35208,18 +34979,18 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B78" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C78" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F78">
         <v>26.091763</v>
@@ -35306,18 +35077,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B79" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C79" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F79">
         <v>7.8346600000000004</v>
@@ -35404,18 +35175,18 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>54</v>
       </c>
       <c r="B80" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C80" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D80" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F80">
         <v>3.3370700000000002</v>
@@ -35502,18 +35273,18 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B81" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C81" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D81" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F81">
         <v>7.7677550000000002</v>
@@ -35600,18 +35371,18 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C82" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D82" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F82">
         <v>3.572155</v>
@@ -35698,18 +35469,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B83" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C83" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D83" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F83">
         <v>9.5338750000000001</v>
@@ -35796,18 +35567,18 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B84" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C84" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D84" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F84">
         <v>26.507746000000001</v>
@@ -35894,23 +35665,23 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B86" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C86" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D86" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F86">
         <v>17.589244999999998</v>
@@ -35997,18 +35768,18 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B87" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C87" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D87" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F87">
         <v>28.823729</v>
@@ -36095,18 +35866,18 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B88" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C88" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D88" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F88">
         <v>28.679842000000001</v>
@@ -36193,18 +35964,18 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B89" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C89" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D89" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F89">
         <v>17.638923999999999</v>
@@ -36291,18 +36062,18 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B90" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C90" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D90" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F90">
         <v>27.283649</v>
@@ -36389,18 +36160,18 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C91" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D91" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F91">
         <v>13.401297</v>
@@ -36487,18 +36258,18 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C92" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D92" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F92">
         <v>14.514303</v>
@@ -36585,18 +36356,18 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D93" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F93">
         <v>42.609589</v>
@@ -36683,23 +36454,23 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="95" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B95" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C95" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D95" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F95">
         <v>26.137505000000001</v>
@@ -36786,18 +36557,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B96" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C96" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D96" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F96">
         <v>17.394409</v>
@@ -36884,18 +36655,18 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>54</v>
       </c>
       <c r="B97" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C97" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F97">
         <v>2.7193990000000001</v>
@@ -36982,18 +36753,18 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B98" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C98" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D98" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F98">
         <v>2.4893969999999999</v>
@@ -37080,18 +36851,18 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>52</v>
       </c>
       <c r="B99" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C99" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D99" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F99">
         <v>0.753328</v>
@@ -37178,18 +36949,18 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B100" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C100" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D100" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F100">
         <v>9.5338750000000001</v>
@@ -37276,23 +37047,23 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="102" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B102" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C102" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D102" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F102">
         <v>23.109310000000001</v>
@@ -37379,18 +37150,18 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B103" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C103" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D103" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F103">
         <v>28.823729</v>
@@ -37477,18 +37248,18 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B104" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C104" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D104" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F104">
         <v>28.684215999999999</v>
@@ -37575,18 +37346,18 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B105" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C105" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F105">
         <v>17.638923999999999</v>
@@ -37673,18 +37444,18 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B106" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F106">
         <v>27.012423999999999</v>
@@ -37771,18 +37542,18 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B107" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C107" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F107">
         <v>13.291615</v>
@@ -37869,18 +37640,18 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>54</v>
       </c>
       <c r="B108" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C108" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F108">
         <v>5.3580649999999999</v>
@@ -37967,18 +37738,18 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B109" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C109" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F109">
         <v>7.7677550000000002</v>
@@ -38065,18 +37836,18 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B110" t="s">
+        <v>259</v>
+      </c>
+      <c r="C110" t="s">
         <v>261</v>
       </c>
-      <c r="C110" t="s">
-        <v>263</v>
-      </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F110">
         <v>2.5446469999999999</v>
@@ -38163,18 +37934,18 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B111" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C111" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D111" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F111">
         <v>9.5735130000000002</v>
@@ -38261,18 +38032,18 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B112" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C112" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D112" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F112">
         <v>38.098598000000003</v>
@@ -38359,28 +38130,28 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="115" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B115" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C115" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D115" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F115">
         <v>321.871307</v>
@@ -38467,18 +38238,18 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B116" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C116" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D116" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F116">
         <v>241.12788399999999</v>
@@ -38565,18 +38336,18 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B117" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C117" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D117" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F117">
         <v>225.60749799999999</v>
@@ -38663,18 +38434,18 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C118" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D118" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F118">
         <v>714.84161400000005</v>
@@ -38761,18 +38532,18 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B119" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D119" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F119">
         <v>1503.4482419999999</v>
@@ -38859,18 +38630,18 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B120" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C120" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F120">
         <v>0.107875</v>
@@ -38957,18 +38728,18 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C121" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D121" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F121">
         <v>1503.5561520000001</v>
@@ -39066,7 +38837,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39075,13 +38846,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F77D40-D131-4E09-8DAE-57D0CDD683B3}">
   <dimension ref="A1:AB34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="2" customWidth="1"/>
-    <col min="2" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" style="2" customWidth="1"/>
+    <col min="2" max="31" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>103</v>
       </c>
@@ -39167,7 +38938,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
@@ -39280,9 +39051,9 @@
         <v>5475.0654336080042</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3" s="5">
         <f>INDEX('AEO Table 10 2025'!$F$18:$AG$18,MATCH(B$1,'AEO Table 10 2025'!$F$5:$AG$5,0))*10^6*'Canada Elec Mix'!F3</f>
@@ -39393,9 +39164,9 @@
         <v>3344770.2603455731</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B4" s="5">
         <f>INDEX('AEO Table 10 2025'!$F$18:$AG$18,MATCH(B$1,'AEO Table 10 2025'!$F$5:$AG$5,0))*10^6*'Canada Elec Mix'!F4</f>
@@ -39506,7 +39277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
@@ -39619,7 +39390,7 @@
         <v>5934906.0595875503</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>72</v>
       </c>
@@ -39732,7 +39503,7 @@
         <v>27582653.10554963</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>71</v>
       </c>
@@ -39845,7 +39616,7 @@
         <v>11653042.280715575</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
@@ -39958,7 +39729,7 @@
         <v>3841564.0308032352</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>74</v>
       </c>
@@ -40071,7 +39842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>75</v>
       </c>
@@ -40184,7 +39955,7 @@
         <v>473161.30819733249</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -40297,7 +40068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>77</v>
       </c>
@@ -40410,7 +40181,7 @@
         <v>353432.71074296214</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>78</v>
       </c>
@@ -40523,7 +40294,7 @@
         <v>927702.17862454022</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -40636,7 +40407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -40749,7 +40520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>100</v>
       </c>
@@ -40862,7 +40633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
@@ -40975,7 +40746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>102</v>
       </c>
@@ -41088,526 +40859,526 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>187</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>188</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>189</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A24" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A25" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>193</v>
-      </c>
       <c r="B25">
         <v>0</v>
       </c>
@@ -41690,7 +41461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>104</v>
       </c>
@@ -41776,7 +41547,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -41889,7 +41660,7 @@
         <v>16184968.999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>107</v>
       </c>
@@ -41975,317 +41746,151 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>106</v>
       </c>
       <c r="B31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(B30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>110.13681138755371</v>
+        <v>95.149006264073691</v>
       </c>
       <c r="C31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(C30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>107.92640565537405</v>
+        <v>93.239400327533261</v>
       </c>
       <c r="D31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(D30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.83752570455681</v>
+        <v>87.115200122824959</v>
       </c>
       <c r="E31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(E30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>95.540198209430116</v>
+        <v>82.538751606960091</v>
       </c>
       <c r="F31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(F30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>95.033376783285618</v>
+        <v>82.100900225179132</v>
       </c>
       <c r="G31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(G30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>96.085152657661482</v>
+        <v>83.00954673490277</v>
       </c>
       <c r="H31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(H30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>97.400587259915014</v>
+        <v>84.145972364380768</v>
       </c>
       <c r="I31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(I30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>99.145759137456636</v>
+        <v>85.653655107471849</v>
       </c>
       <c r="J31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(J30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.67523126190808</v>
+        <v>86.974991279426817</v>
       </c>
       <c r="K31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(K30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.88228651477618</v>
+        <v>88.881702681678604</v>
       </c>
       <c r="L31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(L30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.56961754331238</v>
+        <v>89.475499283520975</v>
       </c>
       <c r="M31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(M30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.02089055366463</v>
+        <v>89.001444994882291</v>
       </c>
       <c r="N31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(N30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.05989561269746</v>
+        <v>88.171225629477988</v>
       </c>
       <c r="O31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(O30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.26503414503112</v>
+        <v>87.48453170931424</v>
       </c>
       <c r="P31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(P30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.77037546297241</v>
+        <v>87.921104401228249</v>
       </c>
       <c r="Q31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(Q30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.11446204371831</v>
+        <v>87.354449989764589</v>
       </c>
       <c r="R31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(R30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.80378097202554</v>
+        <v>87.086047492323431</v>
       </c>
       <c r="S31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(S30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.84947931279949</v>
+        <v>87.125527041965185</v>
       </c>
       <c r="T31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(T30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.33333882593998</v>
+        <v>87.543541248720558</v>
       </c>
       <c r="U31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(U30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.79790200654843</v>
+        <v>87.944885035823944</v>
       </c>
       <c r="V31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(V30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.39755396906273</v>
+        <v>88.462934247697049</v>
       </c>
       <c r="W31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(W30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.86948300065119</v>
+        <v>88.870641514841353</v>
       </c>
       <c r="X31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(X30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.37880500022492</v>
+        <v>89.31065318321393</v>
       </c>
       <c r="Y31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(Y30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.66819506231494</v>
+        <v>89.560662026612079</v>
       </c>
       <c r="Z31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(Z30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>104.40386087436207</v>
+        <v>90.196215844421687</v>
       </c>
       <c r="AA31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(AA30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>105.06715170794153</v>
+        <v>90.769243725690885</v>
       </c>
       <c r="AB31" s="10">
         <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(AB30,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>105.86229069589598</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B33">
-        <v>2024</v>
-      </c>
-      <c r="C33">
-        <v>2025</v>
-      </c>
-      <c r="D33">
-        <v>2026</v>
-      </c>
-      <c r="E33">
-        <v>2027</v>
-      </c>
-      <c r="F33">
-        <v>2028</v>
-      </c>
-      <c r="G33">
-        <v>2029</v>
-      </c>
-      <c r="H33">
-        <v>2030</v>
-      </c>
-      <c r="I33">
-        <v>2031</v>
-      </c>
-      <c r="J33">
-        <v>2032</v>
-      </c>
-      <c r="K33">
-        <v>2033</v>
-      </c>
-      <c r="L33">
-        <v>2034</v>
-      </c>
-      <c r="M33">
-        <v>2035</v>
-      </c>
-      <c r="N33">
-        <v>2036</v>
-      </c>
-      <c r="O33">
-        <v>2037</v>
-      </c>
-      <c r="P33">
-        <v>2038</v>
-      </c>
-      <c r="Q33">
-        <v>2039</v>
-      </c>
-      <c r="R33">
-        <v>2040</v>
-      </c>
-      <c r="S33">
-        <v>2041</v>
-      </c>
-      <c r="T33">
-        <v>2042</v>
-      </c>
-      <c r="U33">
-        <v>2043</v>
-      </c>
-      <c r="V33">
-        <v>2044</v>
-      </c>
-      <c r="W33">
-        <v>2045</v>
-      </c>
-      <c r="X33">
-        <v>2046</v>
-      </c>
-      <c r="Y33">
-        <v>2047</v>
-      </c>
-      <c r="Z33">
-        <v>2048</v>
-      </c>
-      <c r="AA33">
-        <v>2049</v>
-      </c>
-      <c r="AB33">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(B33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>110.13681138755371</v>
-      </c>
-      <c r="C34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(C33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>107.92640565537405</v>
-      </c>
-      <c r="D34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(D33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.83752570455681</v>
-      </c>
-      <c r="E34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(E33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>95.540198209430116</v>
-      </c>
-      <c r="F34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(F33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>95.033376783285618</v>
-      </c>
-      <c r="G34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(G33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>96.085152657661482</v>
-      </c>
-      <c r="H34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(H33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>97.400587259915014</v>
-      </c>
-      <c r="I34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(I33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>99.145759137456636</v>
-      </c>
-      <c r="J34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(J33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.67523126190808</v>
-      </c>
-      <c r="K34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(K33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.88228651477618</v>
-      </c>
-      <c r="L34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(L33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.56961754331238</v>
-      </c>
-      <c r="M34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(M33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.02089055366463</v>
-      </c>
-      <c r="N34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(N33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.05989561269746</v>
-      </c>
-      <c r="O34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(O33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.26503414503112</v>
-      </c>
-      <c r="P34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(P33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.77037546297241</v>
-      </c>
-      <c r="Q34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(Q33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.11446204371831</v>
-      </c>
-      <c r="R34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(R33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.80378097202554</v>
-      </c>
-      <c r="S34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(S33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>100.84947931279949</v>
-      </c>
-      <c r="T34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(T33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.33333882593998</v>
-      </c>
-      <c r="U34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(U33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>101.79790200654843</v>
-      </c>
-      <c r="V34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(V33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.39755396906273</v>
-      </c>
-      <c r="W34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(W33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>102.86948300065119</v>
-      </c>
-      <c r="X34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(X33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.37880500022492</v>
-      </c>
-      <c r="Y34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(Y33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>103.66819506231494</v>
-      </c>
-      <c r="Z34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(Z33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>104.40386087436207</v>
-      </c>
-      <c r="AA34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(AA33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>105.06715170794153</v>
-      </c>
-      <c r="AB34" s="10">
-        <f>INDEX('AEO Table 3 2025'!$54:$54,MATCH(AB33,'AEO Table 3 2025'!$5:$5,0))/10^6*About!$A$60/About!$A$58</f>
-        <v>105.86229069589598</v>
-      </c>
+        <v>91.456177400204723</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A34"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
+      <c r="AA34" s="10"/>
+      <c r="AB34" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/elec/EIaE/Elec Imports and Exports.xlsx
+++ b/InputData/elec/EIaE/Elec Imports and Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\elec\EIaE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\EIaE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2DA93D-0E40-4354-AE62-29D168F0AD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6DAB35-7C71-4D66-8DDB-53E994AA5254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2259,9 +2259,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -2505,7 +2506,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2542,6 +2543,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="38">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
@@ -3737,32 +3739,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="70.19921875" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3770,217 +3772,217 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <v>2021</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>2.931E-7</v>
       </c>
@@ -3988,7 +3990,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>0.88711067149387013</v>
       </c>
@@ -3996,7 +3998,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>0.73199999999999998</v>
       </c>
@@ -4004,7 +4006,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>0.71310900044104586</v>
       </c>
@@ -4028,13 +4030,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.19921875" style="2" customWidth="1"/>
-    <col min="2" max="28" width="11.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="2" customWidth="1"/>
+    <col min="2" max="28" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>446</v>
       </c>
@@ -4120,7 +4122,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -4233,7 +4235,7 @@
         <v>5448.1601019276632</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>199</v>
       </c>
@@ -4346,7 +4348,7 @@
         <v>3328333.5338186654</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>200</v>
       </c>
@@ -4459,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>203</v>
       </c>
@@ -4572,7 +4574,7 @@
         <v>5905740.9988296106</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>204</v>
       </c>
@@ -4685,7 +4687,7 @@
         <v>27447107.614919838</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>205</v>
       </c>
@@ -4798,7 +4800,7 @@
         <v>11595777.400240699</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>206</v>
       </c>
@@ -4911,7 +4913,7 @@
         <v>3822685.9816413792</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>207</v>
       </c>
@@ -5024,7 +5026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -5137,7 +5139,7 @@
         <v>470836.11919462058</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>209</v>
       </c>
@@ -5250,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>210</v>
       </c>
@@ -5363,7 +5365,7 @@
         <v>351695.88687765267</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>201</v>
       </c>
@@ -5476,7 +5478,7 @@
         <v>923143.30437561276</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>211</v>
       </c>
@@ -5589,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>212</v>
       </c>
@@ -5702,7 +5704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>213</v>
       </c>
@@ -5815,7 +5817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>214</v>
       </c>
@@ -5928,7 +5930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>215</v>
       </c>
@@ -6041,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>447</v>
       </c>
@@ -6154,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>448</v>
       </c>
@@ -6267,7 +6269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>449</v>
       </c>
@@ -6380,7 +6382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>450</v>
       </c>
@@ -6493,7 +6495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>451</v>
       </c>
@@ -6606,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>452</v>
       </c>
@@ -6719,7 +6721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>453</v>
       </c>
@@ -6843,12 +6845,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>454</v>
       </c>
@@ -6934,7 +6936,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>455</v>
       </c>
@@ -7058,105 +7060,102 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.265625" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>456</v>
       </c>
       <c r="B1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E1">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F1">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G1">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="H1">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="I1">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="J1">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="K1">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="L1">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="M1">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="N1">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="O1">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="P1">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="Q1">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="R1">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="S1">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="T1">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="U1">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="V1">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="W1">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="X1">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="Y1">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Z1">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AA1">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AB1">
-        <v>2049</v>
-      </c>
-      <c r="AC1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>457</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="24">
         <f>calcs!B31</f>
         <v>95.149006264073691</v>
       </c>
@@ -7264,10 +7263,7 @@
         <f>calcs!AB31</f>
         <v>98.592389659514055</v>
       </c>
-      <c r="AC2" s="10">
-        <f>calcs!AC31</f>
-        <v>0</v>
-      </c>
+      <c r="AC2" s="10"/>
       <c r="AD2" s="10"/>
       <c r="AE2" s="10"/>
     </row>
@@ -7280,32 +7276,32 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AE23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="85.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -7397,17 +7393,17 @@
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -7502,7 +7498,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -7597,7 +7593,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -7692,12 +7688,12 @@
         <v>469</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -7792,7 +7788,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -7887,7 +7883,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -7982,17 +7978,17 @@
         <v>476</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -8087,7 +8083,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -8182,7 +8178,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -8277,12 +8273,12 @@
         <v>485</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -8377,7 +8373,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -8472,7 +8468,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -8575,32 +8571,32 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AE121"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="63.265625" customWidth="1"/>
+    <col min="2" max="2" width="63.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -8692,12 +8688,12 @@
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -8792,7 +8788,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>225</v>
       </c>
@@ -8887,7 +8883,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -8982,7 +8978,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>230</v>
       </c>
@@ -9077,12 +9073,12 @@
         <v>491</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>221</v>
       </c>
@@ -9177,7 +9173,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>225</v>
       </c>
@@ -9272,7 +9268,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>238</v>
       </c>
@@ -9367,7 +9363,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>141</v>
       </c>
@@ -9462,7 +9458,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -9557,12 +9553,12 @@
         <v>521</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>221</v>
       </c>
@@ -9657,7 +9653,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -9752,7 +9748,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>238</v>
       </c>
@@ -9847,7 +9843,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -9942,7 +9938,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>254</v>
       </c>
@@ -10037,7 +10033,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>257</v>
       </c>
@@ -10132,7 +10128,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>260</v>
       </c>
@@ -10227,7 +10223,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>230</v>
       </c>
@@ -10322,12 +10318,12 @@
         <v>521</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>221</v>
       </c>
@@ -10422,7 +10418,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>268</v>
       </c>
@@ -10517,7 +10513,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>271</v>
       </c>
@@ -10612,7 +10608,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>274</v>
       </c>
@@ -10707,7 +10703,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>277</v>
       </c>
@@ -10802,7 +10798,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>238</v>
       </c>
@@ -10897,7 +10893,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>141</v>
       </c>
@@ -10992,7 +10988,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>260</v>
       </c>
@@ -11087,7 +11083,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>230</v>
       </c>
@@ -11182,12 +11178,12 @@
         <v>562</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>225</v>
       </c>
@@ -11282,7 +11278,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>238</v>
       </c>
@@ -11377,7 +11373,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>141</v>
       </c>
@@ -11472,7 +11468,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>295</v>
       </c>
@@ -11567,7 +11563,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>574</v>
       </c>
@@ -11662,7 +11658,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>260</v>
       </c>
@@ -11757,12 +11753,12 @@
         <v>540</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>221</v>
       </c>
@@ -11857,7 +11853,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>268</v>
       </c>
@@ -11952,7 +11948,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>271</v>
       </c>
@@ -12047,7 +12043,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>274</v>
       </c>
@@ -12142,7 +12138,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>225</v>
       </c>
@@ -12237,7 +12233,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>238</v>
       </c>
@@ -12332,7 +12328,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>141</v>
       </c>
@@ -12427,7 +12423,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>254</v>
       </c>
@@ -12522,7 +12518,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>319</v>
       </c>
@@ -12617,7 +12613,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>260</v>
       </c>
@@ -12712,7 +12708,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>230</v>
       </c>
@@ -12807,17 +12803,17 @@
         <v>562</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>220</v>
       </c>
@@ -12912,7 +12908,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>233</v>
       </c>
@@ -13007,7 +13003,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>245</v>
       </c>
@@ -13102,7 +13098,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>265</v>
       </c>
@@ -13197,7 +13193,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>337</v>
       </c>
@@ -13292,7 +13288,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>340</v>
       </c>
@@ -13387,7 +13383,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>343</v>
       </c>
@@ -13482,17 +13478,17 @@
         <v>540</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>221</v>
       </c>
@@ -13587,7 +13583,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>225</v>
       </c>
@@ -13682,7 +13678,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>141</v>
       </c>
@@ -13777,7 +13773,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>230</v>
       </c>
@@ -13872,12 +13868,12 @@
         <v>630</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>221</v>
       </c>
@@ -13972,7 +13968,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>225</v>
       </c>
@@ -14067,7 +14063,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>238</v>
       </c>
@@ -14162,7 +14158,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>141</v>
       </c>
@@ -14257,7 +14253,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -14352,12 +14348,12 @@
         <v>479</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>221</v>
       </c>
@@ -14452,7 +14448,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>225</v>
       </c>
@@ -14547,7 +14543,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>238</v>
       </c>
@@ -14642,7 +14638,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>141</v>
       </c>
@@ -14737,7 +14733,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -14832,7 +14828,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>257</v>
       </c>
@@ -14927,7 +14923,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>260</v>
       </c>
@@ -15022,7 +15018,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>230</v>
       </c>
@@ -15117,12 +15113,12 @@
         <v>656</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>221</v>
       </c>
@@ -15217,7 +15213,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>268</v>
       </c>
@@ -15312,7 +15308,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>271</v>
       </c>
@@ -15407,7 +15403,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -15502,7 +15498,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>277</v>
       </c>
@@ -15597,7 +15593,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>238</v>
       </c>
@@ -15692,7 +15688,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>141</v>
       </c>
@@ -15787,7 +15783,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>230</v>
       </c>
@@ -15882,12 +15878,12 @@
         <v>479</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>225</v>
       </c>
@@ -15982,7 +15978,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>238</v>
       </c>
@@ -16077,7 +16073,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>141</v>
       </c>
@@ -16172,7 +16168,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>295</v>
       </c>
@@ -16267,7 +16263,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>574</v>
       </c>
@@ -16362,7 +16358,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>260</v>
       </c>
@@ -16457,12 +16453,12 @@
         <v>661</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -16557,7 +16553,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>268</v>
       </c>
@@ -16652,7 +16648,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>271</v>
       </c>
@@ -16747,7 +16743,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>274</v>
       </c>
@@ -16842,7 +16838,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -16937,7 +16933,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>238</v>
       </c>
@@ -17032,7 +17028,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>141</v>
       </c>
@@ -17127,7 +17123,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>254</v>
       </c>
@@ -17222,7 +17218,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>319</v>
       </c>
@@ -17317,7 +17313,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>260</v>
       </c>
@@ -17412,7 +17408,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>230</v>
       </c>
@@ -17507,17 +17503,17 @@
         <v>668</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>220</v>
       </c>
@@ -17612,7 +17608,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>233</v>
       </c>
@@ -17707,7 +17703,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>245</v>
       </c>
@@ -17802,7 +17798,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>265</v>
       </c>
@@ -17897,7 +17893,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>337</v>
       </c>
@@ -17992,7 +17988,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>340</v>
       </c>
@@ -18087,7 +18083,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>343</v>
       </c>
@@ -18193,7 +18189,7 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18202,33 +18198,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AG23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.265625" customWidth="1"/>
-    <col min="2" max="2" width="90.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="90.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -18326,17 +18322,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -18434,7 +18430,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -18532,7 +18528,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -18630,12 +18626,12 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -18733,7 +18729,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -18831,7 +18827,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -18929,17 +18925,17 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -19037,7 +19033,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>55</v>
       </c>
@@ -19135,7 +19131,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -19233,12 +19229,12 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -19336,7 +19332,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>55</v>
       </c>
@@ -19434,7 +19430,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -19540,37 +19536,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AU159"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.265625" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -19713,7 +19709,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>135</v>
       </c>
@@ -19856,7 +19852,7 @@
         <v>446455.8</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>136</v>
       </c>
@@ -19999,7 +19995,7 @@
         <v>188617.4</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>137</v>
       </c>
@@ -20142,7 +20138,7 @@
         <v>7658.64</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -20285,7 +20281,7 @@
         <v>62179.97</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -20428,7 +20424,7 @@
         <v>96063.03</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -20571,7 +20567,7 @@
         <v>88.62</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>141</v>
       </c>
@@ -20714,7 +20710,7 @@
         <v>69154.7</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>142</v>
       </c>
@@ -20857,12 +20853,12 @@
         <v>5720.7</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -21005,7 +21001,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>135</v>
       </c>
@@ -21148,7 +21144,7 @@
         <v>52458.85</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -21291,7 +21287,7 @@
         <v>982.55</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>137</v>
       </c>
@@ -21434,7 +21430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -21577,7 +21573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>139</v>
       </c>
@@ -21720,7 +21716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>140</v>
       </c>
@@ -21863,7 +21859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>141</v>
       </c>
@@ -22006,7 +22002,7 @@
         <v>1413.07</v>
       </c>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>142</v>
       </c>
@@ -22149,12 +22145,12 @@
         <v>189.45</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>88</v>
       </c>
@@ -22297,7 +22293,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>135</v>
       </c>
@@ -22440,7 +22436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>136</v>
       </c>
@@ -22583,7 +22579,7 @@
         <v>1885.59</v>
       </c>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>137</v>
       </c>
@@ -22726,7 +22722,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>138</v>
       </c>
@@ -22869,7 +22865,7 @@
         <v>160.61000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>139</v>
       </c>
@@ -23012,7 +23008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>140</v>
       </c>
@@ -23155,7 +23151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>141</v>
       </c>
@@ -23298,7 +23294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>142</v>
       </c>
@@ -23441,12 +23437,12 @@
         <v>48.27</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -23589,7 +23585,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -23732,7 +23728,7 @@
         <v>1207.82</v>
       </c>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -23875,7 +23871,7 @@
         <v>3954</v>
       </c>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>137</v>
       </c>
@@ -24018,7 +24014,7 @@
         <v>200.63</v>
       </c>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>138</v>
       </c>
@@ -24161,7 +24157,7 @@
         <v>528.46</v>
       </c>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>139</v>
       </c>
@@ -24304,7 +24300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>140</v>
       </c>
@@ -24447,7 +24443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -24590,7 +24586,7 @@
         <v>2932.47</v>
       </c>
     </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>142</v>
       </c>
@@ -24733,12 +24729,12 @@
         <v>407.56</v>
       </c>
     </row>
-    <row r="51" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -24881,7 +24877,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>135</v>
       </c>
@@ -25024,7 +25020,7 @@
         <v>3123.74</v>
       </c>
     </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>136</v>
       </c>
@@ -25167,7 +25163,7 @@
         <v>3743.52</v>
       </c>
     </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>137</v>
       </c>
@@ -25310,7 +25306,7 @@
         <v>509.39</v>
       </c>
     </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>138</v>
       </c>
@@ -25453,7 +25449,7 @@
         <v>1042.67</v>
       </c>
     </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>139</v>
       </c>
@@ -25596,7 +25592,7 @@
         <v>5353.24</v>
       </c>
     </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>140</v>
       </c>
@@ -25739,7 +25735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>141</v>
       </c>
@@ -25882,7 +25878,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>142</v>
       </c>
@@ -26025,12 +26021,12 @@
         <v>90.41</v>
       </c>
     </row>
-    <row r="62" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>88</v>
       </c>
@@ -26173,7 +26169,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>135</v>
       </c>
@@ -26316,7 +26312,7 @@
         <v>217546.8</v>
       </c>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -26459,7 +26455,7 @@
         <v>29345.68</v>
       </c>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>137</v>
       </c>
@@ -26602,7 +26598,7 @@
         <v>1557.93</v>
       </c>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -26745,7 +26741,7 @@
         <v>9235.25</v>
       </c>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>139</v>
       </c>
@@ -26888,7 +26884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>140</v>
       </c>
@@ -27031,7 +27027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -27174,7 +27170,7 @@
         <v>186.63</v>
       </c>
     </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>142</v>
       </c>
@@ -27317,12 +27313,12 @@
         <v>402.43</v>
       </c>
     </row>
-    <row r="73" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="74" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -27465,7 +27461,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="75" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>135</v>
       </c>
@@ -27608,7 +27604,7 @@
         <v>42724.63</v>
       </c>
     </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>136</v>
       </c>
@@ -27751,7 +27747,7 @@
         <v>73400.41</v>
       </c>
     </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>137</v>
       </c>
@@ -27894,7 +27890,7 @@
         <v>783.61</v>
       </c>
     </row>
-    <row r="78" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>138</v>
       </c>
@@ -28037,7 +28033,7 @@
         <v>30297.55</v>
       </c>
     </row>
-    <row r="79" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>139</v>
       </c>
@@ -28180,7 +28176,7 @@
         <v>90709.79</v>
       </c>
     </row>
-    <row r="80" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>140</v>
       </c>
@@ -28323,7 +28319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>141</v>
       </c>
@@ -28466,7 +28462,7 @@
         <v>4852.41</v>
       </c>
     </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>142</v>
       </c>
@@ -28609,12 +28605,12 @@
         <v>4029.9</v>
       </c>
     </row>
-    <row r="84" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -28757,7 +28753,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>135</v>
       </c>
@@ -28900,7 +28896,7 @@
         <v>39040.559999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>136</v>
       </c>
@@ -29043,7 +29039,7 @@
         <v>6301.06</v>
       </c>
     </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>137</v>
       </c>
@@ -29186,7 +29182,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>138</v>
       </c>
@@ -29329,7 +29325,7 @@
         <v>2353.86</v>
       </c>
     </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>139</v>
       </c>
@@ -29472,7 +29468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>140</v>
       </c>
@@ -29615,7 +29611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>141</v>
       </c>
@@ -29758,7 +29754,7 @@
         <v>168.86</v>
       </c>
     </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>142</v>
       </c>
@@ -29901,12 +29897,12 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="95" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>88</v>
       </c>
@@ -30049,7 +30045,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="97" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>135</v>
       </c>
@@ -30192,7 +30188,7 @@
         <v>505.55</v>
       </c>
     </row>
-    <row r="98" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>136</v>
       </c>
@@ -30335,7 +30331,7 @@
         <v>35844.17</v>
       </c>
     </row>
-    <row r="99" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>137</v>
       </c>
@@ -30478,7 +30474,7 @@
         <v>1278.17</v>
       </c>
     </row>
-    <row r="100" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>138</v>
       </c>
@@ -30621,7 +30617,7 @@
         <v>8876.16</v>
       </c>
     </row>
-    <row r="101" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>139</v>
       </c>
@@ -30764,7 +30760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>140</v>
       </c>
@@ -30907,7 +30903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>141</v>
       </c>
@@ -31050,7 +31046,7 @@
         <v>49880.18</v>
       </c>
     </row>
-    <row r="104" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>142</v>
       </c>
@@ -31193,12 +31189,12 @@
         <v>19.079999999999998</v>
       </c>
     </row>
-    <row r="106" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="107" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>88</v>
       </c>
@@ -31341,7 +31337,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>135</v>
       </c>
@@ -31484,7 +31480,7 @@
         <v>86796.58</v>
       </c>
     </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -31627,7 +31623,7 @@
         <v>19386.72</v>
       </c>
     </row>
-    <row r="110" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -31770,7 +31766,7 @@
         <v>3129.69</v>
       </c>
     </row>
-    <row r="111" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -31913,7 +31909,7 @@
         <v>8396.49</v>
       </c>
     </row>
-    <row r="112" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -32056,7 +32052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -32199,7 +32195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>141</v>
       </c>
@@ -32342,7 +32338,7 @@
         <v>2433.8200000000002</v>
       </c>
     </row>
-    <row r="115" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>142</v>
       </c>
@@ -32485,12 +32481,12 @@
         <v>171.47</v>
       </c>
     </row>
-    <row r="117" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="118" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -32633,7 +32629,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="119" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>135</v>
       </c>
@@ -32776,7 +32772,7 @@
         <v>2285.31</v>
       </c>
     </row>
-    <row r="120" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>136</v>
       </c>
@@ -32919,7 +32915,7 @@
         <v>13656.86</v>
       </c>
     </row>
-    <row r="121" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>137</v>
       </c>
@@ -33062,7 +33058,7 @@
         <v>112.74</v>
       </c>
     </row>
-    <row r="122" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>138</v>
       </c>
@@ -33205,7 +33201,7 @@
         <v>1251.07</v>
       </c>
     </row>
-    <row r="123" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>139</v>
       </c>
@@ -33348,7 +33344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>140</v>
       </c>
@@ -33491,7 +33487,7 @@
         <v>88.62</v>
       </c>
     </row>
-    <row r="125" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>141</v>
       </c>
@@ -33634,7 +33630,7 @@
         <v>7200.9</v>
       </c>
     </row>
-    <row r="126" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>142</v>
       </c>
@@ -33777,12 +33773,12 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="128" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="129" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>88</v>
       </c>
@@ -33925,7 +33921,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>135</v>
       </c>
@@ -34068,7 +34064,7 @@
         <v>471.9</v>
       </c>
     </row>
-    <row r="131" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>136</v>
       </c>
@@ -34211,7 +34207,7 @@
         <v>64.64</v>
       </c>
     </row>
-    <row r="132" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -34354,7 +34350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>138</v>
       </c>
@@ -34497,7 +34493,7 @@
         <v>10.85</v>
       </c>
     </row>
-    <row r="134" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -34640,7 +34636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -34783,7 +34779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>141</v>
       </c>
@@ -34926,7 +34922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>142</v>
       </c>
@@ -35069,12 +35065,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="140" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>88</v>
       </c>
@@ -35217,7 +35213,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="141" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>135</v>
       </c>
@@ -35360,7 +35356,7 @@
         <v>294.02999999999997</v>
       </c>
     </row>
-    <row r="142" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>136</v>
       </c>
@@ -35503,7 +35499,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="143" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>137</v>
       </c>
@@ -35646,7 +35642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>138</v>
       </c>
@@ -35789,7 +35785,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="145" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -35932,7 +35928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>140</v>
       </c>
@@ -36075,7 +36071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>141</v>
       </c>
@@ -36218,7 +36214,7 @@
         <v>86.34</v>
       </c>
     </row>
-    <row r="148" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>142</v>
       </c>
@@ -36361,12 +36357,12 @@
         <v>31.42</v>
       </c>
     </row>
-    <row r="150" spans="1:47" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="151" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>88</v>
       </c>
@@ -36509,7 +36505,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="152" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>135</v>
       </c>
@@ -36652,7 +36648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>136</v>
       </c>
@@ -36795,7 +36791,7 @@
         <v>26.73</v>
       </c>
     </row>
-    <row r="154" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>137</v>
       </c>
@@ -36938,7 +36934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>138</v>
       </c>
@@ -37081,7 +37077,7 @@
         <v>14.35</v>
       </c>
     </row>
-    <row r="156" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>139</v>
       </c>
@@ -37224,7 +37220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>140</v>
       </c>
@@ -37367,7 +37363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>141</v>
       </c>
@@ -37510,7 +37506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:47" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>142</v>
       </c>
@@ -37677,39 +37673,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.73046875" customWidth="1"/>
-    <col min="2" max="13" width="15.73046875" customWidth="1"/>
-    <col min="14" max="14" width="27.46484375" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>161</v>
       </c>
@@ -37717,7 +37713,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>162</v>
       </c>
@@ -37725,7 +37721,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
@@ -37769,12 +37765,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>167</v>
       </c>
@@ -37819,7 +37815,7 @@
         <v>550012957</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -37864,7 +37860,7 @@
         <v>347385073</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>169</v>
       </c>
@@ -37909,7 +37905,7 @@
         <v>74488277</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>170</v>
       </c>
@@ -37954,7 +37950,7 @@
         <v>98374974</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>171</v>
       </c>
@@ -37999,7 +37995,7 @@
         <v>900163</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>172</v>
       </c>
@@ -38044,7 +38040,7 @@
         <v>19759832</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>173</v>
       </c>
@@ -38088,7 +38084,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>175</v>
       </c>
@@ -38133,7 +38129,7 @@
         <v>12820</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>176</v>
       </c>
@@ -38178,7 +38174,7 @@
         <v>8833017</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>177</v>
       </c>
@@ -38223,7 +38219,7 @@
         <v>258815</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>178</v>
       </c>
@@ -38267,12 +38263,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>174</v>
       </c>
@@ -38280,7 +38276,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>181</v>
       </c>
@@ -38288,12 +38284,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1</v>
       </c>
@@ -38301,7 +38297,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2</v>
       </c>
@@ -38309,7 +38305,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3</v>
       </c>
@@ -38317,7 +38313,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>4</v>
       </c>
@@ -38325,7 +38321,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
@@ -38333,7 +38329,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -38341,7 +38337,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>7</v>
       </c>
@@ -38349,7 +38345,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>8</v>
       </c>
@@ -38357,7 +38353,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9</v>
       </c>
@@ -38365,7 +38361,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>10</v>
       </c>
@@ -38373,7 +38369,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>11</v>
       </c>
@@ -38381,7 +38377,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>12</v>
       </c>
@@ -38389,23 +38385,23 @@
         <v>195</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>198</v>
       </c>
       <c r="B52" s="17"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>199</v>
       </c>
@@ -38414,7 +38410,7 @@
         <v>0.78286526317577265</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>200</v>
       </c>
@@ -38422,7 +38418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>201</v>
       </c>
@@ -38440,12 +38436,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AF20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -38540,7 +38536,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -38669,7 +38665,7 @@
         <v>1.0117144477412501E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>199</v>
       </c>
@@ -38798,7 +38794,7 @@
         <v>6.1806611040571502E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>200</v>
       </c>
@@ -38927,7 +38923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>203</v>
       </c>
@@ -39056,7 +39052,7 @@
         <v>0.10966864742135086</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>204</v>
       </c>
@@ -39185,7 +39181,7 @@
         <v>0.50968831317747454</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>205</v>
       </c>
@@ -39314,7 +39310,7 @@
         <v>0.21533169563912261</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>206</v>
       </c>
@@ -39443,7 +39439,7 @@
         <v>7.0986655392820466E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>207</v>
       </c>
@@ -39541,7 +39537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -39670,7 +39666,7 @@
         <v>8.7433499639461149E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>209</v>
       </c>
@@ -39768,7 +39764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>210</v>
       </c>
@@ -39897,7 +39893,7 @@
         <v>6.5309352755510818E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>201</v>
       </c>
@@ -40026,7 +40022,7 @@
         <v>1.7142620644388807E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>211</v>
       </c>
@@ -40124,7 +40120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>212</v>
       </c>
@@ -40222,7 +40218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>213</v>
       </c>
@@ -40320,7 +40316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>214</v>
       </c>
@@ -40418,7 +40414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>215</v>
       </c>
@@ -40516,7 +40512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>216</v>
       </c>
@@ -40653,33 +40649,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AG121"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.46484375" customWidth="1"/>
-    <col min="2" max="2" width="54.53125" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="54.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -40777,12 +40773,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -40880,7 +40876,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>225</v>
       </c>
@@ -40978,7 +40974,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -41076,7 +41072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>230</v>
       </c>
@@ -41174,12 +41170,12 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>221</v>
       </c>
@@ -41277,7 +41273,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>225</v>
       </c>
@@ -41375,7 +41371,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>238</v>
       </c>
@@ -41473,7 +41469,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>141</v>
       </c>
@@ -41571,7 +41567,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -41669,12 +41665,12 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>221</v>
       </c>
@@ -41772,7 +41768,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -41870,7 +41866,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>238</v>
       </c>
@@ -41968,7 +41964,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -42066,7 +42062,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>254</v>
       </c>
@@ -42164,7 +42160,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>257</v>
       </c>
@@ -42262,7 +42258,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>260</v>
       </c>
@@ -42360,7 +42356,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>230</v>
       </c>
@@ -42458,12 +42454,12 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>221</v>
       </c>
@@ -42561,7 +42557,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>268</v>
       </c>
@@ -42659,7 +42655,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>271</v>
       </c>
@@ -42757,7 +42753,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>274</v>
       </c>
@@ -42855,7 +42851,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>277</v>
       </c>
@@ -42953,7 +42949,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>238</v>
       </c>
@@ -43051,7 +43047,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>141</v>
       </c>
@@ -43149,7 +43145,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>260</v>
       </c>
@@ -43247,7 +43243,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>230</v>
       </c>
@@ -43345,12 +43341,12 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>225</v>
       </c>
@@ -43448,7 +43444,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>238</v>
       </c>
@@ -43546,7 +43542,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>141</v>
       </c>
@@ -43644,7 +43640,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>295</v>
       </c>
@@ -43742,7 +43738,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -43840,7 +43836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>260</v>
       </c>
@@ -43938,12 +43934,12 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>221</v>
       </c>
@@ -44041,7 +44037,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>268</v>
       </c>
@@ -44139,7 +44135,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>271</v>
       </c>
@@ -44237,7 +44233,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>274</v>
       </c>
@@ -44335,7 +44331,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>225</v>
       </c>
@@ -44433,7 +44429,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>238</v>
       </c>
@@ -44531,7 +44527,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>141</v>
       </c>
@@ -44629,7 +44625,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>254</v>
       </c>
@@ -44727,7 +44723,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>319</v>
       </c>
@@ -44825,7 +44821,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>260</v>
       </c>
@@ -44923,7 +44919,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="s">
         <v>230</v>
       </c>
@@ -45021,17 +45017,17 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>220</v>
       </c>
@@ -45129,7 +45125,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>233</v>
       </c>
@@ -45227,7 +45223,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>245</v>
       </c>
@@ -45325,7 +45321,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>265</v>
       </c>
@@ -45423,7 +45419,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>337</v>
       </c>
@@ -45521,7 +45517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>340</v>
       </c>
@@ -45619,7 +45615,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>343</v>
       </c>
@@ -45717,17 +45713,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>221</v>
       </c>
@@ -45825,7 +45821,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>225</v>
       </c>
@@ -45923,7 +45919,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>141</v>
       </c>
@@ -46021,7 +46017,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>230</v>
       </c>
@@ -46119,12 +46115,12 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>221</v>
       </c>
@@ -46222,7 +46218,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>225</v>
       </c>
@@ -46320,7 +46316,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>238</v>
       </c>
@@ -46418,7 +46414,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>141</v>
       </c>
@@ -46516,7 +46512,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -46614,12 +46610,12 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>221</v>
       </c>
@@ -46717,7 +46713,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>225</v>
       </c>
@@ -46815,7 +46811,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>238</v>
       </c>
@@ -46913,7 +46909,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>141</v>
       </c>
@@ -47011,7 +47007,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -47109,7 +47105,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>257</v>
       </c>
@@ -47207,7 +47203,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>260</v>
       </c>
@@ -47305,7 +47301,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>230</v>
       </c>
@@ -47403,12 +47399,12 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>221</v>
       </c>
@@ -47506,7 +47502,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>268</v>
       </c>
@@ -47604,7 +47600,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>271</v>
       </c>
@@ -47702,7 +47698,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -47800,7 +47796,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>277</v>
       </c>
@@ -47898,7 +47894,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>238</v>
       </c>
@@ -47996,7 +47992,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>141</v>
       </c>
@@ -48094,7 +48090,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>230</v>
       </c>
@@ -48192,12 +48188,12 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>225</v>
       </c>
@@ -48295,7 +48291,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>238</v>
       </c>
@@ -48393,7 +48389,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>141</v>
       </c>
@@ -48491,7 +48487,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>295</v>
       </c>
@@ -48589,7 +48585,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -48687,7 +48683,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>260</v>
       </c>
@@ -48785,12 +48781,12 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -48888,7 +48884,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>268</v>
       </c>
@@ -48986,7 +48982,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>271</v>
       </c>
@@ -49084,7 +49080,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>274</v>
       </c>
@@ -49182,7 +49178,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -49280,7 +49276,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>238</v>
       </c>
@@ -49378,7 +49374,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>141</v>
       </c>
@@ -49476,7 +49472,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>254</v>
       </c>
@@ -49574,7 +49570,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>319</v>
       </c>
@@ -49672,7 +49668,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>260</v>
       </c>
@@ -49770,7 +49766,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>230</v>
       </c>
@@ -49868,17 +49864,17 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>220</v>
       </c>
@@ -49976,7 +49972,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>233</v>
       </c>
@@ -50074,7 +50070,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>245</v>
       </c>
@@ -50172,7 +50168,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>265</v>
       </c>
@@ -50270,7 +50266,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>337</v>
       </c>
@@ -50368,7 +50364,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>340</v>
       </c>
@@ -50466,7 +50462,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>343</v>
       </c>
@@ -50575,7 +50571,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -50584,13 +50580,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AB34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.19921875" style="2" customWidth="1"/>
-    <col min="2" max="31" width="11.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="2" customWidth="1"/>
+    <col min="2" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>446</v>
       </c>
@@ -50676,7 +50672,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -50789,7 +50785,7 @@
         <v>5448.1601019276632</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>199</v>
       </c>
@@ -50902,7 +50898,7 @@
         <v>3328333.5338186654</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>200</v>
       </c>
@@ -51015,7 +51011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>203</v>
       </c>
@@ -51128,7 +51124,7 @@
         <v>5905740.9988296106</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>204</v>
       </c>
@@ -51241,7 +51237,7 @@
         <v>27447107.614919838</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>205</v>
       </c>
@@ -51354,7 +51350,7 @@
         <v>11595777.400240699</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>206</v>
       </c>
@@ -51467,7 +51463,7 @@
         <v>3822685.9816413792</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>207</v>
       </c>
@@ -51580,7 +51576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -51693,7 +51689,7 @@
         <v>470836.11919462058</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>209</v>
       </c>
@@ -51806,7 +51802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>210</v>
       </c>
@@ -51919,7 +51915,7 @@
         <v>351695.88687765267</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>201</v>
       </c>
@@ -52032,7 +52028,7 @@
         <v>923143.30437561276</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>211</v>
       </c>
@@ -52145,7 +52141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>212</v>
       </c>
@@ -52258,7 +52254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>213</v>
       </c>
@@ -52371,7 +52367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>214</v>
       </c>
@@ -52484,7 +52480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>215</v>
       </c>
@@ -52597,7 +52593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>447</v>
       </c>
@@ -52683,7 +52679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>448</v>
       </c>
@@ -52769,7 +52765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>449</v>
       </c>
@@ -52855,7 +52851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>450</v>
       </c>
@@ -52941,7 +52937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>451</v>
       </c>
@@ -53027,7 +53023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>452</v>
       </c>
@@ -53113,7 +53109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>453</v>
       </c>
@@ -53199,7 +53195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="29.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:28" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>454</v>
       </c>
@@ -53285,7 +53281,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>455</v>
       </c>
@@ -53398,7 +53394,7 @@
         <v>17994251</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>456</v>
       </c>
@@ -53484,7 +53480,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>457</v>
       </c>
@@ -53597,10 +53593,10 @@
         <v>98.592389659514055</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
